--- a/攒机/清单.xlsx
+++ b/攒机/清单.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25635" windowHeight="12705" activeTab="1"/>
+    <workbookView windowWidth="26550" windowHeight="12390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
   <si>
     <t>供电</t>
   </si>
@@ -70,6 +70,9 @@
   </si>
   <si>
     <t>风扇</t>
+  </si>
+  <si>
+    <t>机箱</t>
   </si>
   <si>
     <t>型号</t>
@@ -130,14 +133,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -595,152 +591,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -748,16 +744,10 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1089,17 +1079,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:2">
+    <row r="2" spans="1:2">
       <c r="B2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:2">
+    <row r="3" spans="1:2">
       <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:2">
+    <row r="4" spans="1:2">
       <c r="B4" t="s">
         <v>4</v>
       </c>
@@ -1113,7 +1103,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="6.625" style="1" customWidth="1"/>
@@ -1135,190 +1125,193 @@
     <col min="17" max="17" width="6.625" style="1" customWidth="1"/>
     <col min="18" max="18" width="16.625" customWidth="1"/>
     <col min="19" max="19" width="6.625" style="1" customWidth="1"/>
+    <col min="20" max="21" width="5.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:21">
+      <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3" t="s">
+      <c r="E1" s="2"/>
+      <c r="F1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="3"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="3" t="s">
+      <c r="G1" s="2"/>
+      <c r="I1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="3"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="3" t="s">
+      <c r="J1" s="2"/>
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="2"/>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="2"/>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="5"/>
+      <c r="T1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="U1" s="3"/>
     </row>
-    <row r="2" spans="1:19">
-      <c r="A2" s="2"/>
+    <row r="2" spans="1:21">
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="I2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="L2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="N2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="P2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="R2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="T2" t="s">
+        <v>15</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:21">
       <c r="A3" s="1">
         <f>C3+E3+H3+K3+M3*2+O3*2+Q3+S3*4</f>
         <v>18866</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="1">
         <v>2771</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" s="1">
         <v>725</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" s="1">
         <v>4277</v>
       </c>
       <c r="I3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K3" s="1">
         <v>4985</v>
       </c>
       <c r="L3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M3" s="1">
         <v>1252</v>
       </c>
       <c r="N3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O3" s="1">
         <v>844</v>
       </c>
       <c r="P3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q3" s="1">
         <v>1196</v>
       </c>
       <c r="R3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S3" s="1">
         <v>180</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:21">
       <c r="A4" s="1">
         <f>C4+E4+H3+K3+M4*2+O3*2+Q3+S3*4</f>
         <v>17358</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" s="1">
         <v>2586</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E4" s="1">
         <v>516</v>
       </c>
       <c r="L4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M4" s="1">
         <v>695</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:H1"/>
@@ -1327,6 +1320,7 @@
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="R1:S1"/>
+    <mergeCell ref="T1:U1"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
